--- a/03_bloques/B04/B04_trabajo.xlsx
+++ b/03_bloques/B04/B04_trabajo.xlsx
@@ -587,7 +587,7 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -877,7 +877,7 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1794,7 +1794,7 @@
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -2033,7 +2033,7 @@
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2323,7 +2323,7 @@
       <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2613,7 +2613,7 @@
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2903,7 +2903,7 @@
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3287,7 +3287,7 @@
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3385,7 +3385,7 @@
       <c r="G60" s="3" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -3628,7 +3628,7 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3675,7 +3675,7 @@
       <c r="G66" s="3" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3722,7 +3722,7 @@
       <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       <c r="G69" s="3" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3867,7 +3867,7 @@
       <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -4012,7 +4012,7 @@
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       <c r="G75" s="3" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       <c r="G79" s="5" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4353,7 +4353,7 @@
       <c r="G80" s="3" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       <c r="G82" s="3" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       <c r="G85" s="5" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4643,7 +4643,7 @@
       <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       <c r="G91" s="5" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4929,7 +4929,7 @@
       <c r="G92" s="3" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       <c r="G93" s="3" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       <c r="G95" s="3" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       <c r="G97" s="5" t="inlineStr"/>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -5215,7 +5215,7 @@
       <c r="G98" s="3" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       <c r="G99" s="3" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       <c r="G101" s="3" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5407,7 +5407,7 @@
       <c r="G102" s="3" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5454,7 +5454,7 @@
       <c r="G103" s="3" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       <c r="G105" s="3" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I106" s="4" t="inlineStr">
@@ -5650,7 +5650,7 @@
       <c r="G107" s="5" t="inlineStr"/>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5697,7 +5697,7 @@
       <c r="G108" s="3" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       <c r="G109" s="3" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       <c r="G111" s="3" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -5940,7 +5940,7 @@
       <c r="G113" s="5" t="inlineStr"/>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -5987,7 +5987,7 @@
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6034,7 +6034,7 @@
       <c r="G115" s="3" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       <c r="G119" s="5" t="inlineStr"/>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
@@ -6277,7 +6277,7 @@
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6324,7 +6324,7 @@
       <c r="G121" s="3" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       <c r="G123" s="3" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -6520,7 +6520,7 @@
       <c r="G125" s="5" t="inlineStr"/>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
@@ -6567,7 +6567,7 @@
       <c r="G126" s="3" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       <c r="G128" s="3" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       <c r="G131" s="5" t="inlineStr"/>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
@@ -6857,7 +6857,7 @@
       <c r="G132" s="3" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -6904,7 +6904,7 @@
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -6951,7 +6951,7 @@
       <c r="G134" s="3" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr">
@@ -7100,7 +7100,7 @@
       <c r="G137" s="5" t="inlineStr"/>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
@@ -7147,7 +7147,7 @@
       <c r="G138" s="3" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       <c r="G140" s="3" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr">
@@ -7390,7 +7390,7 @@
       <c r="G143" s="5" t="inlineStr"/>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
@@ -7437,7 +7437,7 @@
       <c r="G144" s="3" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       <c r="G146" s="3" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       <c r="G148" s="5" t="inlineStr"/>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr">
@@ -7727,7 +7727,7 @@
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       <c r="G152" s="3" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       <c r="G154" s="3" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
@@ -8064,7 +8064,7 @@
       <c r="G157" s="5" t="inlineStr"/>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
@@ -8111,7 +8111,7 @@
       <c r="G158" s="3" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       <c r="G160" s="3" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       <c r="G161" s="3" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I162" s="4" t="inlineStr">
@@ -8354,7 +8354,7 @@
       <c r="G163" s="5" t="inlineStr"/>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
@@ -8452,7 +8452,7 @@
       <c r="G165" s="3" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       <c r="G166" s="3" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       <c r="G167" s="3" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I168" s="4" t="inlineStr">
@@ -8695,7 +8695,7 @@
       <c r="G170" s="3" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       <c r="G171" s="3" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
@@ -8789,7 +8789,7 @@
       <c r="G172" s="3" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
@@ -8887,7 +8887,7 @@
       <c r="G174" s="5" t="inlineStr"/>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
@@ -8985,7 +8985,7 @@
       <c r="G176" s="3" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -9032,7 +9032,7 @@
       <c r="G177" s="3" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       <c r="G180" s="5" t="inlineStr"/>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
@@ -9228,7 +9228,7 @@
       <c r="G181" s="3" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       <c r="G182" s="3" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -9322,7 +9322,7 @@
       <c r="G183" s="3" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       <c r="G186" s="5" t="inlineStr"/>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -9518,7 +9518,7 @@
       <c r="G187" s="3" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       <c r="G188" s="3" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9663,7 +9663,7 @@
       <c r="G190" s="3" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       <c r="G192" s="5" t="inlineStr"/>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I192" s="4" t="inlineStr">
@@ -9808,7 +9808,7 @@
       <c r="G193" s="3" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       <c r="G194" s="3" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -9953,7 +9953,7 @@
       <c r="G196" s="3" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -10000,7 +10000,7 @@
       <c r="G197" s="5" t="inlineStr"/>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
@@ -10047,7 +10047,7 @@
       <c r="G198" s="3" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -10094,7 +10094,7 @@
       <c r="G199" s="3" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       <c r="G201" s="3" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
   <autoFilter ref="A1:K201"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Borrador,Sin borrador,Revisar_Juan,Enviado,Validado,Grabado"</formula1>
+      <formula1>"Borrador,Sin borrador,Por_revisar,Enviado,Validado,Grabado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Revisar_Juan</t>
+          <t>Por_revisar</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Español redactado o adaptado por Claude (Revisar_Juan)</t>
+          <t>Español redactado o adaptado por Claude (Por_revisar)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
